--- a/08_RTM/BharatBites_RTM.xlsx
+++ b/08_RTM/BharatBites_RTM.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="1" r:id="R9a4f88f4bb2c4974"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="1" r:id="R1506ba224a634c14"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -45,7 +45,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="15">
+  <x:cellXfs count="16">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -79,6 +79,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -298,13 +299,13 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="55" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="62" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="45" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="46" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -2075,10 +2076,62 @@
         <x:v>Covered</x:v>
       </x:c>
     </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="12" t="str">
+        <x:v>BB_REQ_010</x:v>
+      </x:c>
+      <x:c r="B69" s="12" t="str">
+        <x:v>Users should be able to search for food items or restaurants.</x:v>
+      </x:c>
+      <x:c r="C69" s="12" t="str">
+        <x:v>BB_TS_012</x:v>
+      </x:c>
+      <x:c r="D69" s="12" t="str">
+        <x:v>BB_TC_009</x:v>
+      </x:c>
+      <x:c r="E69" s="12" t="str">
+        <x:v>Search food items and restaurants with relevant results</x:v>
+      </x:c>
+      <x:c r="F69" s="12" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="G69" s="12" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="H69" s="12" t="str">
+        <x:v>Covered</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="12" t="str">
+        <x:v>BB_REQ_011</x:v>
+      </x:c>
+      <x:c r="B70" s="12" t="str">
+        <x:v>System should display relevant results matching the search term.</x:v>
+      </x:c>
+      <x:c r="C70" s="12" t="str">
+        <x:v>BB_TS_013</x:v>
+      </x:c>
+      <x:c r="D70" s="12" t="str">
+        <x:v>BB_TC_009</x:v>
+      </x:c>
+      <x:c r="E70" s="12" t="str">
+        <x:v>Search food items and restaurants with relevant results</x:v>
+      </x:c>
+      <x:c r="F70" s="12" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="G70" s="12" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="H70" s="12" t="str">
+        <x:v>Covered</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2066677d2304237"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R986f579479764fe2"/>
   </x:tableParts>
 </x:worksheet>
 </file>